--- a/RfidBarcode.Crm/wwwroot/assets/doc/TemplateImportFinish.xlsx
+++ b/RfidBarcode.Crm/wwwroot/assets/doc/TemplateImportFinish.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\BEKA\2025\Triputra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C6F403-2310-42B8-AE3E-39B4D631036F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746008A7-96BA-4360-86A8-E70D51595CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C441D291-5D15-4CCB-B100-FD2A976459A4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>Merk</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Kp</t>
   </si>
   <si>
-    <t>Ib</t>
-  </si>
-  <si>
     <t>Kode1</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>Oz</t>
   </si>
   <si>
-    <t>T01</t>
-  </si>
-  <si>
     <t>Grade</t>
   </si>
   <si>
@@ -87,18 +81,12 @@
     <t>Serial Number</t>
   </si>
   <si>
-    <t>K3l</t>
-  </si>
-  <si>
     <t>Inisial</t>
   </si>
   <si>
     <t>Tanggal Buat Barcode</t>
   </si>
   <si>
-    <t>Point Grade</t>
-  </si>
-  <si>
     <t>SINARAN</t>
   </si>
   <si>
@@ -130,6 +118,54 @@
   </si>
   <si>
     <t>2025-02-20</t>
+  </si>
+  <si>
+    <t>oz1</t>
+  </si>
+  <si>
+    <t>oz2</t>
+  </si>
+  <si>
+    <t>grade1</t>
+  </si>
+  <si>
+    <t>grade2</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>1"</t>
+  </si>
+  <si>
+    <t>2"</t>
+  </si>
+  <si>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>0001</t>
+  </si>
+  <si>
+    <t>0002</t>
+  </si>
+  <si>
+    <t>000x</t>
+  </si>
+  <si>
+    <t>000y</t>
+  </si>
+  <si>
+    <t>100.1</t>
+  </si>
+  <si>
+    <t>88.89</t>
   </si>
 </sst>
 </file>
@@ -491,21 +527,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A60F6917-92C0-44E9-92B8-D129CAC9A8DB}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="6" width="9.06640625" style="2"/>
-    <col min="7" max="7" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="9.06640625" style="2"/>
-    <col min="16" max="16" width="11.19921875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.9296875" style="2" customWidth="1"/>
-    <col min="18" max="19" width="9.06640625" style="2"/>
-    <col min="20" max="20" width="18" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.19921875" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="5" width="9.06640625" style="2"/>
+    <col min="6" max="6" width="10.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="9.06640625" style="2"/>
+    <col min="14" max="14" width="11.19921875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="15.9296875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.06640625" style="2"/>
+    <col min="17" max="17" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,75 +592,111 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
